--- a/data/trans_camb/IP28_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP28_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,93</t>
+          <t>0,0; 7,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,75</t>
+          <t>0,0; 7,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,64</t>
+          <t>0,0; 6,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 2,98</t>
+          <t>-8,32; 3,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 2,48</t>
+          <t>-8,43; 2,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 1,49</t>
+          <t>-8,59; 2,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 3,49</t>
+          <t>-3,32; 3,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 2,49</t>
+          <t>-4,17; 2,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 2,41</t>
+          <t>-4,37; 1,89</t>
         </is>
       </c>
     </row>
@@ -798,22 +798,22 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 252,64</t>
+          <t>-100,0; 382,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 253,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 236,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-82,01; 439,09</t>
+          <t>-85,6; 330,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 3,2</t>
+          <t>-3,97; 2,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 0,56</t>
+          <t>-5,85; 0,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 0,4</t>
+          <t>-5,62; 0,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 3,87</t>
+          <t>-1,08; 3,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,46</t>
+          <t>-0,6; 4,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,62</t>
+          <t>-1,2; 3,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 2,3</t>
+          <t>-1,9; 1,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,32</t>
+          <t>-2,34; 1,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,71</t>
+          <t>-2,81; 0,67</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-85,41; 559,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 632,89</t>
+          <t>-100,0; 324,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,75</t>
+          <t>0,0; 8,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1119,37 +1119,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 5,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 2,3</t>
+          <t>-3,61; 2,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 0,0</t>
+          <t>-5,41; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 0,0</t>
+          <t>-5,4; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 3,69</t>
+          <t>-1,02; 3,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,0</t>
+          <t>-3,21; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,14</t>
+          <t>-1,86; 1,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 5,03</t>
+          <t>-2,56; 4,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 2,38</t>
+          <t>-3,38; 2,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 10,84</t>
+          <t>-1,07; 10,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 5,32</t>
+          <t>-1,53; 5,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,8</t>
+          <t>-1,54; 3,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,0</t>
+          <t>-3,48; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,07</t>
+          <t>-1,86; 3,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,83</t>
+          <t>-2,05; 1,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 4,54</t>
+          <t>-1,05; 5,29</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 6,0</t>
+          <t>-3,13; 6,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 4,99</t>
+          <t>-3,09; 5,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 0,0</t>
+          <t>-8,57; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 7,93</t>
+          <t>-2,86; 7,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 0,0</t>
+          <t>-7,48; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 7,32</t>
+          <t>-2,99; 6,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 5,93</t>
+          <t>-1,99; 5,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 2,09</t>
+          <t>-3,75; 1,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 3,28</t>
+          <t>-3,0; 2,85</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,22 +1757,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 9,9</t>
+          <t>-0,97; 9,58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 3,61</t>
+          <t>-2,34; 3,6</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 0,0</t>
+          <t>-5,79; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,03</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,1</t>
+          <t>0,0; 7,16</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,2; 6,75</t>
+          <t>0,23; 6,74</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,91</t>
+          <t>-1,67; 1,86</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,1</t>
+          <t>-1,12; 2,75</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,1</t>
+          <t>-1,74; 1,1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 4,11</t>
+          <t>-0,62; 4,17</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 5,85</t>
+          <t>-0,47; 5,77</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,49</t>
+          <t>-2,69; 1,87</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 3,16</t>
+          <t>-1,62; 3,2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,16</t>
+          <t>-2,14; 2,18</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,01</t>
+          <t>-1,4; 1,21</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,88</t>
+          <t>-0,57; 2,89</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,03</t>
+          <t>-0,52; 2,85</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-67,94; 1022,06</t>
+          <t>-58,0; 1054,34</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-78,51; 1054,74</t>
+          <t>-64,19; 1000,44</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,04</t>
+          <t>-2,5; 3,14</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,27; -0,25</t>
+          <t>-4,64; -0,19</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,65; -0,8</t>
+          <t>-5,34; -0,78</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 2,71</t>
+          <t>-1,23; 2,76</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,7</t>
+          <t>-1,67; 1,72</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,77</t>
+          <t>-1,66; 1,73</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,2</t>
+          <t>-1,19; 2,11</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,32</t>
+          <t>-2,2; 0,25</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,12</t>
+          <t>-2,47; 0,06</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-76,46; 364,19</t>
+          <t>-82,88; 335,52</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-52,88; 303,39</t>
+          <t>-59,02; 273,99</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 119,31</t>
+          <t>-100,0; 72,35</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 91,43</t>
+          <t>-100,0; 113,17</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,88</t>
+          <t>-0,42; 1,95</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,61</t>
+          <t>-1,27; 0,61</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,27</t>
+          <t>-0,86; 1,44</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,52</t>
+          <t>-0,49; 1,54</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,65</t>
+          <t>-1,16; 0,61</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,65</t>
+          <t>-1,16; 0,67</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,36</t>
+          <t>-0,17; 1,36</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,42</t>
+          <t>-0,95; 0,29</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,58</t>
+          <t>-0,76; 0,65</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 223,74</t>
+          <t>-24,75; 230,13</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-70,93; 81,44</t>
+          <t>-67,71; 78,22</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-56,6; 145,41</t>
+          <t>-49,61; 169,36</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 189,97</t>
+          <t>-35,59; 211,18</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-65,58; 98,17</t>
+          <t>-71,45; 85,67</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-66,68; 90,76</t>
+          <t>-69,3; 100,05</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 142,12</t>
+          <t>-12,79; 145,75</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-56,02; 48,87</t>
+          <t>-58,49; 31,81</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-50,67; 62,43</t>
+          <t>-47,76; 65,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP28_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP28_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,91</t>
+          <t>0,0; 8,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,94</t>
+          <t>0,0; 6,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,55</t>
+          <t>0,0; 6,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 3,54</t>
+          <t>-8,25; 3,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 2,47</t>
+          <t>-7,93; 3,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 2,08</t>
+          <t>-8,17; 1,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 3,31</t>
+          <t>-3,33; 3,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 2,53</t>
+          <t>-4,09; 2,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 1,89</t>
+          <t>-3,92; 2,5</t>
         </is>
       </c>
     </row>
@@ -798,22 +798,22 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 382,46</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 253,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 236,35</t>
+          <t>-100,0; 225,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-85,6; 330,72</t>
+          <t>-77,85; 490,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,48; 386,59</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 2,73</t>
+          <t>-4,32; 2,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 0,24</t>
+          <t>-5,54; 0,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 0,41</t>
+          <t>-6,47; 0,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,34</t>
+          <t>-0,6; 3,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,04</t>
+          <t>-1,11; 3,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,0</t>
+          <t>-1,21; 2,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,94</t>
+          <t>-1,88; 2,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,13</t>
+          <t>-2,46; 1,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,67</t>
+          <t>-2,73; 0,81</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 324,65</t>
+          <t>-100,0; 325,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,57</t>
+          <t>0,0; 7,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1119,37 +1119,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,86</t>
+          <t>0,0; 5,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 2,2</t>
+          <t>-4,32; 2,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 0,0</t>
+          <t>-6,19; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 0,0</t>
+          <t>-6,27; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 3,54</t>
+          <t>-1,16; 3,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,0</t>
+          <t>-2,78; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,14</t>
+          <t>-2,28; 1,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 4,64</t>
+          <t>-3,03; 4,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 2,97</t>
+          <t>-3,4; 2,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 10,61</t>
+          <t>-1,18; 9,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 5,55</t>
+          <t>-1,53; 4,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,61</t>
+          <t>-1,56; 2,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 0,0</t>
+          <t>-4,44; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 3,0</t>
+          <t>-1,62; 3,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 1,91</t>
+          <t>-2,04; 1,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 5,29</t>
+          <t>-1,05; 4,91</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 6,12</t>
+          <t>-3,09; 6,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 5,08</t>
+          <t>-3,12; 5,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 0,0</t>
+          <t>-7,75; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 7,74</t>
+          <t>-2,96; 7,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 0,0</t>
+          <t>-5,99; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 6,72</t>
+          <t>-2,98; 7,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 5,48</t>
+          <t>-2,19; 5,09</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,64</t>
+          <t>-3,08; 1,63</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,85</t>
+          <t>-3,04; 3,05</t>
         </is>
       </c>
     </row>
@@ -1757,22 +1757,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 9,58</t>
+          <t>-1,02; 10,53</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 3,6</t>
+          <t>-2,34; 3,66</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 0,0</t>
+          <t>-5,78; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,8</t>
+          <t>0,0; 9,15</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,16</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,74</t>
+          <t>0,21; 6,69</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,86</t>
+          <t>-1,56; 1,92</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,75</t>
+          <t>-1,12; 2,97</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,1</t>
+          <t>-2,32; 1,09</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,17</t>
+          <t>-0,61; 3,88</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 5,77</t>
+          <t>-0,33; 5,92</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,87</t>
+          <t>-2,25; 1,88</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 3,2</t>
+          <t>-2,13; 3,22</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 2,18</t>
+          <t>-2,16; 2,22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,21</t>
+          <t>-1,46; 1,03</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,89</t>
+          <t>-0,55; 2,97</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,85</t>
+          <t>-0,68; 2,97</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-58,0; 1054,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-64,19; 1000,44</t>
+          <t>-75,25; —</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,14</t>
+          <t>-2,27; 3,06</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,64; -0,19</t>
+          <t>-4,07; -0,06</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,34; -0,78</t>
+          <t>-4,6; -0,79</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,76</t>
+          <t>-1,25; 2,87</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,72</t>
+          <t>-1,62; 1,68</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,73</t>
+          <t>-1,67; 1,75</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,11</t>
+          <t>-1,21; 2,2</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,25</t>
+          <t>-2,34; 0,29</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,06</t>
+          <t>-2,39; 0,17</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-82,88; 335,52</t>
+          <t>-77,01; 393,26</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-59,02; 273,99</t>
+          <t>-57,28; 311,56</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 72,35</t>
+          <t>-92,44; 151,62</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 113,17</t>
+          <t>-100,0; 173,5</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,95</t>
+          <t>-0,46; 1,8</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,61</t>
+          <t>-1,31; 0,57</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,44</t>
+          <t>-1,04; 1,35</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,54</t>
+          <t>-0,57; 1,45</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,61</t>
+          <t>-1,17; 0,72</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,67</t>
+          <t>-1,21; 0,67</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,36</t>
+          <t>-0,25; 1,35</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,29</t>
+          <t>-0,87; 0,41</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,65</t>
+          <t>-0,8; 0,65</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 230,13</t>
+          <t>-24,71; 241,5</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-67,71; 78,22</t>
+          <t>-68,68; 70,9</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-49,61; 169,36</t>
+          <t>-59,15; 185,97</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 211,18</t>
+          <t>-33,66; 181,56</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-71,45; 85,67</t>
+          <t>-66,43; 103,37</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-69,3; 100,05</t>
+          <t>-69,64; 104,99</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 145,75</t>
+          <t>-15,53; 141,25</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-58,49; 31,81</t>
+          <t>-53,93; 48,68</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 65,16</t>
+          <t>-50,51; 67,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP28_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP28_R-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,31</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-2,09</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2,5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,34</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,77</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,66</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,31</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,45</t>
+          <t>2,07</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-0,21</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>-7,99; 2,98</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>-8,16; 2,48</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>-8,44; 2,32</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 8,93</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,52</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,12</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-8,25; 3,63</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 3,53</t>
+          <t>0,0; 7,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 1,9</t>
+          <t>0,0; 7,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 3,65</t>
+          <t>-3,39; 3,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 2,64</t>
+          <t>-3,96; 2,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 2,5</t>
+          <t>-3,53; 3,0</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-35,28%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-49,08%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-44,33%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-35,28%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-49,08%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-52,02%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>8,76%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-21,26%</t>
+          <t>-7,99%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 252,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 225,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-77,85; 490,35</t>
+          <t>-82,01; 439,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-86,48; 386,59</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,72</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,72</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,25</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,68</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,71</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>-1,52</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 2,96</t>
+          <t>-1,18; 3,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 0,59</t>
+          <t>-1,13; 3,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 0,47</t>
+          <t>-1,2; 3,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,56</t>
+          <t>-4,22; 3,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,48</t>
+          <t>-5,52; 0,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,68</t>
+          <t>-5,25; 0,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,29</t>
+          <t>-1,9; 2,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,26</t>
+          <t>-2,35; 1,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 0,81</t>
+          <t>-2,53; 1,01</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>120,66%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>120,62%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>42,25%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-28,63%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-73,44%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-74,92%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>120,66%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>120,62%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>-66,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-51,6%</t>
+          <t>-42,64%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,41; 559,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 325,44</t>
+          <t>-100,0; 632,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,76</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,8</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-1,8</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>2,49</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,12</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,8</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>-0,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,82</t>
+          <t>-3,85; 2,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,16; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,73</t>
+          <t>-6,29; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 2,23</t>
+          <t>0,0; 8,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 0,0</t>
+          <t>0,0; 5,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,58</t>
+          <t>-1,31; 3,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,0</t>
+          <t>-3,0; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,11</t>
+          <t>-1,85; 1,25</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-42,42%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-42,42%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,55%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-43,67%</t>
+          <t>-39,89%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,59</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,77</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,33</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,64</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,63</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,59</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 4,7</t>
+          <t>-1,54; 5,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 2,41</t>
+          <t>-1,56; 2,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 9,83</t>
+          <t>-3,6; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,58</t>
+          <t>-2,65; 5,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,9</t>
+          <t>-4,03; 2,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,0</t>
+          <t>-0,56; 11,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 3,09</t>
+          <t>-1,65; 3,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,94</t>
+          <t>-2,03; 1,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 4,91</t>
+          <t>-0,96; 5,06</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>76,56%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19,25%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>19,53%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-37,93%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>215,23%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>76,56%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>19,25%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>230,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>106,5%</t>
+          <t>126,59%</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1488,34 +1488,34 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,53</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,48</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,64</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,45</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>-1,53</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,48</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1,03</t>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,39</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 6,63</t>
+          <t>-2,06; 7,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 5,0</t>
+          <t>-6,25; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 0,0</t>
+          <t>-2,97; 7,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 7,79</t>
+          <t>-3,11; 6,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 0,0</t>
+          <t>-3,14; 4,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 7,48</t>
+          <t>-7,7; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 5,09</t>
+          <t>-1,49; 5,93</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,63</t>
+          <t>-3,03; 2,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 3,05</t>
+          <t>-3,02; 3,2</t>
         </is>
       </c>
     </row>
@@ -1594,34 +1594,34 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>103,46%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>43,26%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>29,26%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>6,36%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>103,46%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>42,36%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>68,14%</t>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-24,19%</t>
+          <t>-25,8%</t>
         </is>
       </c>
     </row>
@@ -1704,34 +1704,34 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>2,58</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>2,91</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>0,03</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>-1,16</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2,58</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>2,75</t>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,11</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 10,53</t>
+          <t>0,0; 8,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 3,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 0,0</t>
+          <t>0,0; 6,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,15</t>
+          <t>-0,94; 9,9</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,33; 3,61</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>-6,19; 0,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,21; 6,69</t>
+          <t>0,2; 6,75</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,92</t>
+          <t>-1,13; 1,91</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,97</t>
+          <t>-1,13; 2,62</t>
         </is>
       </c>
     </row>
@@ -1810,34 +1810,34 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>251,71%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2,69%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>492,16%</t>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,1</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,54</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-0,04</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1,48</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,46</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>1,25</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,09</t>
+          <t>-2,23; 1,49</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,88</t>
+          <t>-1,62; 3,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 5,92</t>
+          <t>-2,02; 2,76</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,88</t>
+          <t>-1,77; 1,1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 3,22</t>
+          <t>-0,61; 4,11</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,22</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,03</t>
+          <t>-1,45; 1,01</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,97</t>
+          <t>-0,59; 2,88</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,97</t>
+          <t>-0,46; 3,68</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-9,38%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>49,93%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>16,6%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-6,47%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>255,9%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>336,14%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-9,38%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>49,93%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>424,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>106,17%</t>
+          <t>149,39%</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-67,94; 1022,06</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-75,25; —</t>
+          <t>-72,45; 1267,52</t>
         </is>
       </c>
     </row>
@@ -2136,34 +2136,34 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>0,74</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0,02</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>0,28</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-1,73</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>-2,11</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
           <t>0,51</t>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,0</t>
+          <t>-1,08</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 3,06</t>
+          <t>-0,92; 2,71</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,07; -0,06</t>
+          <t>-1,67; 1,7</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,6; -0,79</t>
+          <t>-1,69; 1,29</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,87</t>
+          <t>-2,45; 3,04</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,68</t>
+          <t>-4,27; -0,25</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,75</t>
+          <t>-4,65; -0,8</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,2</t>
+          <t>-1,11; 2,2</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,29</t>
+          <t>-2,29; 0,32</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,17</t>
+          <t>-2,6; -0,05</t>
         </is>
       </c>
     </row>
@@ -2242,34 +2242,34 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-15,29%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>13,36%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-82,18%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>88,78%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
           <t>35,05%</t>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-68,59%</t>
+          <t>-74,25%</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-77,01; 393,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-76,46; 364,19</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-57,28; 311,56</t>
+          <t>-52,88; 303,39</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-92,44; 151,62</t>
+          <t>-100,0; 119,31</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 173,5</t>
+          <t>-100,0; 57,93</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>0,43</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,23</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-0,22</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>0,7</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-0,31</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>0,43</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-0,23</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,03</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,8</t>
+          <t>-0,58; 1,52</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,57</t>
+          <t>-1,17; 0,65</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,35</t>
+          <t>-1,08; 0,7</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,45</t>
+          <t>-0,39; 1,88</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,72</t>
+          <t>-1,28; 0,61</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,67</t>
+          <t>-0,79; 1,62</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,35</t>
+          <t>-0,16; 1,36</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,41</t>
+          <t>-0,86; 0,42</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,65</t>
+          <t>-0,71; 0,75</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>34,55%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-18,93%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-18,07%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>53,31%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-23,6%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>34,55%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-18,93%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-20,2%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-6,05%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 241,5</t>
+          <t>-37,97; 189,97</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-68,68; 70,9</t>
+          <t>-65,58; 98,17</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-59,15; 185,97</t>
+          <t>-65,21; 103,72</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-33,66; 181,56</t>
+          <t>-28,36; 223,74</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-66,43; 103,37</t>
+          <t>-70,93; 81,44</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-69,64; 104,99</t>
+          <t>-48,76; 184,05</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 141,25</t>
+          <t>-12,35; 142,12</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-53,93; 48,68</t>
+          <t>-56,02; 48,87</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-50,51; 67,59</t>
+          <t>-45,56; 78,14</t>
         </is>
       </c>
     </row>
